--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/200.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/200.xlsx
@@ -426,13 +426,13 @@
         <v>-10.97756790979141</v>
       </c>
       <c r="E2">
-        <v>-11.0744667749976</v>
+        <v>-10.22743382575889</v>
       </c>
       <c r="F2">
-        <v>0.622439331651048</v>
+        <v>-1.070808354547515</v>
       </c>
       <c r="G2">
-        <v>-4.920958256972451</v>
+        <v>-4.531747349556955</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.13580832166692</v>
       </c>
       <c r="E3">
-        <v>-10.9272868412743</v>
+        <v>-14.09889418202639</v>
       </c>
       <c r="F3">
-        <v>0.2723864783378052</v>
+        <v>-0.9563491769209599</v>
       </c>
       <c r="G3">
-        <v>-6.195084608126213</v>
+        <v>-3.910311604198204</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.18841044609091</v>
       </c>
       <c r="E4">
-        <v>-12.4257407765164</v>
+        <v>-13.43368399266966</v>
       </c>
       <c r="F4">
-        <v>0.5768571079928698</v>
+        <v>-1.191175547091617</v>
       </c>
       <c r="G4">
-        <v>-5.22016536281178</v>
+        <v>-3.966759716188316</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.10817379547746</v>
       </c>
       <c r="E5">
-        <v>-13.14697724629603</v>
+        <v>-13.46609428114255</v>
       </c>
       <c r="F5">
-        <v>0.5651582723955186</v>
+        <v>-0.4390585626432268</v>
       </c>
       <c r="G5">
-        <v>-5.882274470666018</v>
+        <v>-3.720991436443902</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.88548113201998</v>
       </c>
       <c r="E6">
-        <v>-14.13882626582603</v>
+        <v>-12.11639166010442</v>
       </c>
       <c r="F6">
-        <v>0.9741471576459251</v>
+        <v>-0.874707553274141</v>
       </c>
       <c r="G6">
-        <v>-6.363309979704279</v>
+        <v>-3.899770827201164</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.51487095760473</v>
       </c>
       <c r="E7">
-        <v>-12.88864591805447</v>
+        <v>-15.06120849407837</v>
       </c>
       <c r="F7">
-        <v>0.692847729239655</v>
+        <v>-1.486782966590925</v>
       </c>
       <c r="G7">
-        <v>-5.822823693871786</v>
+        <v>-1.483082515169815</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.00255825860078</v>
       </c>
       <c r="E8">
-        <v>-13.79468035513911</v>
+        <v>-15.02813251992634</v>
       </c>
       <c r="F8">
-        <v>0.9673182177385502</v>
+        <v>-0.6758637733552256</v>
       </c>
       <c r="G8">
-        <v>-7.201440793881565</v>
+        <v>-5.328807535774043</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.356042872973106</v>
       </c>
       <c r="E9">
-        <v>-15.79698589389663</v>
+        <v>-13.38715845071485</v>
       </c>
       <c r="F9">
-        <v>0.868917818094551</v>
+        <v>-0.3785554537027359</v>
       </c>
       <c r="G9">
-        <v>-5.140331557132256</v>
+        <v>-4.961221111821067</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.590737126021729</v>
       </c>
       <c r="E10">
-        <v>-16.16413192406851</v>
+        <v>-16.36915405629177</v>
       </c>
       <c r="F10">
-        <v>1.291054629854936</v>
+        <v>-0.6897212001153208</v>
       </c>
       <c r="G10">
-        <v>-5.529029329989164</v>
+        <v>-3.263543564372949</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.728735289779972</v>
       </c>
       <c r="E11">
-        <v>-16.22419760330624</v>
+        <v>-17.3761327074814</v>
       </c>
       <c r="F11">
-        <v>0.9603214050041388</v>
+        <v>-0.6311280405088499</v>
       </c>
       <c r="G11">
-        <v>-3.486164509706779</v>
+        <v>-3.47503114505821</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.798925060228612</v>
       </c>
       <c r="E12">
-        <v>-16.56272367774964</v>
+        <v>-18.13202106036773</v>
       </c>
       <c r="F12">
-        <v>0.7261704854064164</v>
+        <v>-0.09132900590793371</v>
       </c>
       <c r="G12">
-        <v>-3.315247664605286</v>
+        <v>-3.667731379808107</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.831788218620993</v>
       </c>
       <c r="E13">
-        <v>-17.56637390054363</v>
+        <v>-19.79587298026597</v>
       </c>
       <c r="F13">
-        <v>1.081094818115551</v>
+        <v>-0.6361832297909326</v>
       </c>
       <c r="G13">
-        <v>-3.100952741302723</v>
+        <v>-3.458488348998472</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.870047391369482</v>
       </c>
       <c r="E14">
-        <v>-18.61297669930038</v>
+        <v>-20.11718632500621</v>
       </c>
       <c r="F14">
-        <v>0.7409005341259187</v>
+        <v>-0.2407556182944342</v>
       </c>
       <c r="G14">
-        <v>-2.402934145984011</v>
+        <v>-2.428047944444922</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.950339987391049</v>
       </c>
       <c r="E15">
-        <v>-19.46258182177544</v>
+        <v>-20.18121441900066</v>
       </c>
       <c r="F15">
-        <v>1.229879237753341</v>
+        <v>-0.0604673287337652</v>
       </c>
       <c r="G15">
-        <v>-1.870955962187445</v>
+        <v>-0.9200116876684146</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.105562195325883</v>
       </c>
       <c r="E16">
-        <v>-21.81660035128669</v>
+        <v>-21.67888945671343</v>
       </c>
       <c r="F16">
-        <v>1.390400501930452</v>
+        <v>-0.1343788838073242</v>
       </c>
       <c r="G16">
-        <v>-1.758665568040906</v>
+        <v>-0.1973030437178181</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.362350475381315</v>
       </c>
       <c r="E17">
-        <v>-21.5163942238962</v>
+        <v>-22.82747349012292</v>
       </c>
       <c r="F17">
-        <v>1.355302411432483</v>
+        <v>0.01152556662323893</v>
       </c>
       <c r="G17">
-        <v>-0.3250272011684398</v>
+        <v>-0.5902217621372975</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.7391382690184</v>
       </c>
       <c r="E18">
-        <v>-21.10297624631395</v>
+        <v>-21.9293095408636</v>
       </c>
       <c r="F18">
-        <v>1.910754003448645</v>
+        <v>0.2019345288365237</v>
       </c>
       <c r="G18">
-        <v>0.1672840259765784</v>
+        <v>0.1976781445726272</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.244901503398209</v>
       </c>
       <c r="E19">
-        <v>-22.05730233021639</v>
+        <v>-22.77244347398171</v>
       </c>
       <c r="F19">
-        <v>1.706223135587387</v>
+        <v>0.1792914935105282</v>
       </c>
       <c r="G19">
-        <v>0.324829577644955</v>
+        <v>-0.7510844804360237</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.8867668384422212</v>
       </c>
       <c r="E20">
-        <v>-24.20520736526853</v>
+        <v>-23.81603936599736</v>
       </c>
       <c r="F20">
-        <v>1.903324838999319</v>
+        <v>1.099282096848458</v>
       </c>
       <c r="G20">
-        <v>1.284457413113494</v>
+        <v>1.847839431895586</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6632332891380122</v>
       </c>
       <c r="E21">
-        <v>-23.83720998198321</v>
+        <v>-23.87944253057875</v>
       </c>
       <c r="F21">
-        <v>2.11577582014369</v>
+        <v>0.6703622726522457</v>
       </c>
       <c r="G21">
-        <v>2.448607441452668</v>
+        <v>1.696855381486045</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5655722493252707</v>
       </c>
       <c r="E22">
-        <v>-25.18597520890176</v>
+        <v>-25.7799298597478</v>
       </c>
       <c r="F22">
-        <v>1.993318927644165</v>
+        <v>1.13922316003584</v>
       </c>
       <c r="G22">
-        <v>1.910282941857319</v>
+        <v>0.6632765797612662</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.5806459737113097</v>
       </c>
       <c r="E23">
-        <v>-25.09553252602057</v>
+        <v>-25.85838114345669</v>
       </c>
       <c r="F23">
-        <v>2.602649778609493</v>
+        <v>1.379297139757306</v>
       </c>
       <c r="G23">
-        <v>1.51259372731575</v>
+        <v>2.544172959534809</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.6922055700249516</v>
       </c>
       <c r="E24">
-        <v>-25.51862785255721</v>
+        <v>-28.06297361613684</v>
       </c>
       <c r="F24">
-        <v>2.721708038214484</v>
+        <v>1.318821745670335</v>
       </c>
       <c r="G24">
-        <v>1.460561883075025</v>
+        <v>2.335830397111855</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.882205513404073</v>
       </c>
       <c r="E25">
-        <v>-26.5663220135498</v>
+        <v>-27.82453134573696</v>
       </c>
       <c r="F25">
-        <v>2.295665807666626</v>
+        <v>1.52171822902686</v>
       </c>
       <c r="G25">
-        <v>1.418706655822019</v>
+        <v>0.4392817580286384</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.134735058883166</v>
       </c>
       <c r="E26">
-        <v>-27.13502136485507</v>
+        <v>-27.13026646714701</v>
       </c>
       <c r="F26">
-        <v>2.436387580488913</v>
+        <v>1.41958503454017</v>
       </c>
       <c r="G26">
-        <v>2.061624531185101</v>
+        <v>1.882845140427839</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.433621630963415</v>
       </c>
       <c r="E27">
-        <v>-27.62521509076336</v>
+        <v>-24.86324445179712</v>
       </c>
       <c r="F27">
-        <v>2.836048437897381</v>
+        <v>1.737883000542937</v>
       </c>
       <c r="G27">
-        <v>1.999896099059851</v>
+        <v>1.905896469017785</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.761780371534954</v>
       </c>
       <c r="E28">
-        <v>-27.28271301614123</v>
+        <v>-26.99233820582139</v>
       </c>
       <c r="F28">
-        <v>2.206644114453859</v>
+        <v>1.811024874541592</v>
       </c>
       <c r="G28">
-        <v>2.104227941729982</v>
+        <v>3.244191124359241</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.103099645685186</v>
       </c>
       <c r="E29">
-        <v>-27.48661208681059</v>
+        <v>-25.24062030475232</v>
       </c>
       <c r="F29">
-        <v>2.79420376019964</v>
+        <v>0.5519477895018805</v>
       </c>
       <c r="G29">
-        <v>1.583753903682384</v>
+        <v>1.796866962227428</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.442532951600673</v>
       </c>
       <c r="E30">
-        <v>-25.9834938233406</v>
+        <v>-27.64937449959428</v>
       </c>
       <c r="F30">
-        <v>2.460794072351751</v>
+        <v>1.795243245094238</v>
       </c>
       <c r="G30">
-        <v>1.160245744480039</v>
+        <v>1.451941222490763</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.765432921855827</v>
       </c>
       <c r="E31">
-        <v>-26.83127849926458</v>
+        <v>-27.3045447893322</v>
       </c>
       <c r="F31">
-        <v>2.670226510021294</v>
+        <v>1.488238685974471</v>
       </c>
       <c r="G31">
-        <v>1.709246753439537</v>
+        <v>0.8865993607494219</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.062013132483672</v>
       </c>
       <c r="E32">
-        <v>-26.06297307064922</v>
+        <v>-23.70457550677256</v>
       </c>
       <c r="F32">
-        <v>2.029509775223787</v>
+        <v>2.072569155358671</v>
       </c>
       <c r="G32">
-        <v>0.6539011147940502</v>
+        <v>1.61129764256912</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.324339290564281</v>
       </c>
       <c r="E33">
-        <v>-26.68864515344499</v>
+        <v>-26.05592676509329</v>
       </c>
       <c r="F33">
-        <v>2.5335558569307</v>
+        <v>1.716550481861967</v>
       </c>
       <c r="G33">
-        <v>0.8050738662993298</v>
+        <v>0.07924999899627903</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.546677038173444</v>
       </c>
       <c r="E34">
-        <v>-26.28857258876335</v>
+        <v>-24.75479202778742</v>
       </c>
       <c r="F34">
-        <v>3.023828448291037</v>
+        <v>1.828135233252</v>
       </c>
       <c r="G34">
-        <v>1.185064904387955</v>
+        <v>0.425652242043459</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.726083952829468</v>
       </c>
       <c r="E35">
-        <v>-25.48370878948406</v>
+        <v>-27.10598478951788</v>
       </c>
       <c r="F35">
-        <v>2.986402310097371</v>
+        <v>1.444531570120173</v>
       </c>
       <c r="G35">
-        <v>0.1241674808731105</v>
+        <v>-0.3172010715136027</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.862544413177665</v>
       </c>
       <c r="E36">
-        <v>-25.19193920916986</v>
+        <v>-24.37826299947165</v>
       </c>
       <c r="F36">
-        <v>2.957040402425124</v>
+        <v>1.974987531672954</v>
       </c>
       <c r="G36">
-        <v>0.5106902253107179</v>
+        <v>0.04250294351036886</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.956971263661501</v>
       </c>
       <c r="E37">
-        <v>-23.10091633612807</v>
+        <v>-23.65907792841749</v>
       </c>
       <c r="F37">
-        <v>3.042782240687016</v>
+        <v>1.688165720739546</v>
       </c>
       <c r="G37">
-        <v>0.1767554967644333</v>
+        <v>-0.3144202132606149</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.014005218682056</v>
       </c>
       <c r="E38">
-        <v>-22.68948183016118</v>
+        <v>-26.36413017758133</v>
       </c>
       <c r="F38">
-        <v>3.204172959411704</v>
+        <v>2.086866852363258</v>
       </c>
       <c r="G38">
-        <v>0.1948575597731682</v>
+        <v>0.6427313341445492</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.040115056175465</v>
       </c>
       <c r="E39">
-        <v>-22.00928692031307</v>
+        <v>-21.0433181297369</v>
       </c>
       <c r="F39">
-        <v>3.084650673973488</v>
+        <v>3.044741284904414</v>
       </c>
       <c r="G39">
-        <v>-0.2134386426762259</v>
+        <v>-0.2128261917514607</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.04233347164555</v>
       </c>
       <c r="E40">
-        <v>-21.4933669335672</v>
+        <v>-22.52318267917751</v>
       </c>
       <c r="F40">
-        <v>3.459969971461653</v>
+        <v>2.418466364349801</v>
       </c>
       <c r="G40">
-        <v>-0.8038347130587709</v>
+        <v>-1.446580440053811</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.027325373651245</v>
       </c>
       <c r="E41">
-        <v>-21.92782420138908</v>
+        <v>-20.78225613166871</v>
       </c>
       <c r="F41">
-        <v>3.333792953766761</v>
+        <v>2.354365867422389</v>
       </c>
       <c r="G41">
-        <v>-0.826164342721155</v>
+        <v>-2.185351850960951</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.00201791750753</v>
       </c>
       <c r="E42">
-        <v>-21.44297407480984</v>
+        <v>-19.52918208900625</v>
       </c>
       <c r="F42">
-        <v>3.379942144142666</v>
+        <v>2.445908820452535</v>
       </c>
       <c r="G42">
-        <v>-0.1305690667371895</v>
+        <v>0.2645313011926695</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.972411176507055</v>
       </c>
       <c r="E43">
-        <v>-19.23277535130819</v>
+        <v>-19.37983754470729</v>
       </c>
       <c r="F43">
-        <v>3.471399577053379</v>
+        <v>2.435125366874308</v>
       </c>
       <c r="G43">
-        <v>-1.539027424237959</v>
+        <v>-1.401209413438099</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.943802970634217</v>
       </c>
       <c r="E44">
-        <v>-18.56719835555683</v>
+        <v>-20.45717056808008</v>
       </c>
       <c r="F44">
-        <v>3.900113519480584</v>
+        <v>2.661484453368068</v>
       </c>
       <c r="G44">
-        <v>-0.85952802066593</v>
+        <v>-1.756877873449699</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.923653641806365</v>
       </c>
       <c r="E45">
-        <v>-17.86976354516151</v>
+        <v>-17.84062281492216</v>
       </c>
       <c r="F45">
-        <v>4.041088685249341</v>
+        <v>2.45805426111804</v>
       </c>
       <c r="G45">
-        <v>-0.8648149618921461</v>
+        <v>-1.420791290302889</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.918188970680762</v>
       </c>
       <c r="E46">
-        <v>-16.48543621186073</v>
+        <v>-17.01364194858941</v>
       </c>
       <c r="F46">
-        <v>4.094508669483029</v>
+        <v>3.185573917140783</v>
       </c>
       <c r="G46">
-        <v>-2.209012319930122</v>
+        <v>-1.629289448366188</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.931950636579859</v>
       </c>
       <c r="E47">
-        <v>-16.63030209536611</v>
+        <v>-17.82520336092604</v>
       </c>
       <c r="F47">
-        <v>3.935339890157703</v>
+        <v>2.048221260614705</v>
       </c>
       <c r="G47">
-        <v>-1.711281729737317</v>
+        <v>-1.982627284318141</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.967498957113249</v>
       </c>
       <c r="E48">
-        <v>-15.18505772971414</v>
+        <v>-15.21777595441956</v>
       </c>
       <c r="F48">
-        <v>4.171845780451684</v>
+        <v>2.459158104141101</v>
       </c>
       <c r="G48">
-        <v>-1.56232373319781</v>
+        <v>-2.83768822838326</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.025413252652869</v>
       </c>
       <c r="E49">
-        <v>-14.61829203681015</v>
+        <v>-15.52328492487304</v>
       </c>
       <c r="F49">
-        <v>3.562711309019871</v>
+        <v>2.676250927323625</v>
       </c>
       <c r="G49">
-        <v>-1.524841736602182</v>
+        <v>-2.347571892930779</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.102510138128513</v>
       </c>
       <c r="E50">
-        <v>-14.49154457780947</v>
+        <v>-14.50428317519304</v>
       </c>
       <c r="F50">
-        <v>4.163749875811957</v>
+        <v>2.348189414352175</v>
       </c>
       <c r="G50">
-        <v>-2.237526048659865</v>
+        <v>-0.8598921806752499</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.19669621487484</v>
       </c>
       <c r="E51">
-        <v>-13.37086952970926</v>
+        <v>-14.53420733143573</v>
       </c>
       <c r="F51">
-        <v>3.676727048990103</v>
+        <v>2.913138490743227</v>
       </c>
       <c r="G51">
-        <v>-2.1442514280909</v>
+        <v>-2.019976859092198</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.305834694665376</v>
       </c>
       <c r="E52">
-        <v>-12.62018439345774</v>
+        <v>-13.52820683063176</v>
       </c>
       <c r="F52">
-        <v>4.181962493839511</v>
+        <v>3.181499041820357</v>
       </c>
       <c r="G52">
-        <v>-2.836698375267018</v>
+        <v>-0.4402970863003233</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.424818197502161</v>
       </c>
       <c r="E53">
-        <v>-12.53062023453404</v>
+        <v>-11.00856389276397</v>
       </c>
       <c r="F53">
-        <v>4.108739850839168</v>
+        <v>3.445323859155669</v>
       </c>
       <c r="G53">
-        <v>-2.232017300882518</v>
+        <v>1.00316366918716</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.548087682387897</v>
       </c>
       <c r="E54">
-        <v>-11.23085309637849</v>
+        <v>-11.07421318045317</v>
       </c>
       <c r="F54">
-        <v>4.246617287837327</v>
+        <v>3.716923088829872</v>
       </c>
       <c r="G54">
-        <v>-2.248672655490591</v>
+        <v>-1.173215452694032</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.670177398385217</v>
       </c>
       <c r="E55">
-        <v>-9.204238709147795</v>
+        <v>-13.35463947886577</v>
       </c>
       <c r="F55">
-        <v>4.304143821509749</v>
+        <v>2.764699318995003</v>
       </c>
       <c r="G55">
-        <v>-3.190095801038678</v>
+        <v>-0.4340831923231112</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.78447295300438</v>
       </c>
       <c r="E56">
-        <v>-8.144340310704532</v>
+        <v>-10.82777815342976</v>
       </c>
       <c r="F56">
-        <v>4.232063030474438</v>
+        <v>3.25056128938084</v>
       </c>
       <c r="G56">
-        <v>-2.493901316312105</v>
+        <v>-0.9478699283813816</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.888486741895799</v>
       </c>
       <c r="E57">
-        <v>-8.962585750676482</v>
+        <v>-10.92129114168815</v>
       </c>
       <c r="F57">
-        <v>3.67911369380467</v>
+        <v>2.93005246992012</v>
       </c>
       <c r="G57">
-        <v>-2.628574308849656</v>
+        <v>-1.67842787580559</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.983301808335878</v>
       </c>
       <c r="E58">
-        <v>-7.492448363404354</v>
+        <v>-10.36980904856004</v>
       </c>
       <c r="F58">
-        <v>3.930009136046334</v>
+        <v>3.244693658964137</v>
       </c>
       <c r="G58">
-        <v>-3.079189214927554</v>
+        <v>-1.874041390630046</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.069192984477032</v>
       </c>
       <c r="E59">
-        <v>-7.660391350452817</v>
+        <v>-9.479465773911977</v>
       </c>
       <c r="F59">
-        <v>3.757169807258935</v>
+        <v>2.688584828993068</v>
       </c>
       <c r="G59">
-        <v>-3.86562917105466</v>
+        <v>-1.955970771635929</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.146084566368533</v>
       </c>
       <c r="E60">
-        <v>-8.435213253165216</v>
+        <v>-10.61740336492942</v>
       </c>
       <c r="F60">
-        <v>3.403658140226372</v>
+        <v>2.923641628374422</v>
       </c>
       <c r="G60">
-        <v>-2.252360603221339</v>
+        <v>-1.82223797403153</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.21308319813981</v>
       </c>
       <c r="E61">
-        <v>-8.290510394724116</v>
+        <v>-8.424267931488675</v>
       </c>
       <c r="F61">
-        <v>3.849648730485105</v>
+        <v>2.930977354174737</v>
       </c>
       <c r="G61">
-        <v>-3.518889252362475</v>
+        <v>-3.39844829509825</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.267028383802364</v>
       </c>
       <c r="E62">
-        <v>-8.653825335885502</v>
+        <v>-7.188999848624371</v>
       </c>
       <c r="F62">
-        <v>3.926950999923621</v>
+        <v>3.221058431882119</v>
       </c>
       <c r="G62">
-        <v>-3.417858023594996</v>
+        <v>-2.578465891567248</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.304854179384296</v>
       </c>
       <c r="E63">
-        <v>-7.175074791050784</v>
+        <v>-6.157780276071685</v>
       </c>
       <c r="F63">
-        <v>3.756834061604861</v>
+        <v>2.48785643903478</v>
       </c>
       <c r="G63">
-        <v>-3.209601535356064</v>
+        <v>-4.672210486242692</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.326034702426831</v>
       </c>
       <c r="E64">
-        <v>-6.57598937915405</v>
+        <v>-5.781753908370769</v>
       </c>
       <c r="F64">
-        <v>3.052371580005002</v>
+        <v>2.554106024889443</v>
       </c>
       <c r="G64">
-        <v>-3.360933193047229</v>
+        <v>-1.461775844079066</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.330682996074441</v>
       </c>
       <c r="E65">
-        <v>-5.824221937614702</v>
+        <v>-6.838781254293169</v>
       </c>
       <c r="F65">
-        <v>3.227450268956833</v>
+        <v>2.402467767192031</v>
       </c>
       <c r="G65">
-        <v>-2.598186811344686</v>
+        <v>-2.426167554578616</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.31823486004944</v>
       </c>
       <c r="E66">
-        <v>-5.385942637730341</v>
+        <v>-7.232052051015293</v>
       </c>
       <c r="F66">
-        <v>2.802822287791462</v>
+        <v>1.666576641700276</v>
       </c>
       <c r="G66">
-        <v>-2.444163680130094</v>
+        <v>-2.728668653229521</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.288842428082235</v>
       </c>
       <c r="E67">
-        <v>-5.492474988760787</v>
+        <v>-5.836679769609803</v>
       </c>
       <c r="F67">
-        <v>2.959892656778831</v>
+        <v>1.570957229643788</v>
       </c>
       <c r="G67">
-        <v>-3.442150806762168</v>
+        <v>-4.061745888801085</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.24305267552444</v>
       </c>
       <c r="E68">
-        <v>-4.093099536332516</v>
+        <v>-6.435321391053786</v>
       </c>
       <c r="F68">
-        <v>2.486122281057374</v>
+        <v>0.940973269835215</v>
       </c>
       <c r="G68">
-        <v>-3.207042483654207</v>
+        <v>-3.348634516368836</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.180771553420378</v>
       </c>
       <c r="E69">
-        <v>-5.449404672473834</v>
+        <v>-5.830557272751433</v>
       </c>
       <c r="F69">
-        <v>2.989740762167118</v>
+        <v>1.063251203566295</v>
       </c>
       <c r="G69">
-        <v>-2.875809160267968</v>
+        <v>-2.590185222776268</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.104484511383267</v>
       </c>
       <c r="E70">
-        <v>-5.498574843249119</v>
+        <v>-4.206528753276643</v>
       </c>
       <c r="F70">
-        <v>2.582436940010739</v>
+        <v>1.188306957473055</v>
       </c>
       <c r="G70">
-        <v>-2.848510401751138</v>
+        <v>-1.254178154402448</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.018039407798206</v>
       </c>
       <c r="E71">
-        <v>-5.781894291065007</v>
+        <v>-6.590009534681798</v>
       </c>
       <c r="F71">
-        <v>2.117631923476585</v>
+        <v>1.211463905368611</v>
       </c>
       <c r="G71">
-        <v>-3.819410644780895</v>
+        <v>-3.601023887191793</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.922558314297424</v>
       </c>
       <c r="E72">
-        <v>-5.705249868485186</v>
+        <v>-5.541713086646187</v>
       </c>
       <c r="F72">
-        <v>2.120015400879321</v>
+        <v>1.058286285521392</v>
       </c>
       <c r="G72">
-        <v>-2.54075215678387</v>
+        <v>-4.865533103553973</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.818767141001257</v>
       </c>
       <c r="E73">
-        <v>-4.848580326558154</v>
+        <v>-5.189610647127793</v>
       </c>
       <c r="F73">
-        <v>1.641278523407046</v>
+        <v>0.2931100620942881</v>
       </c>
       <c r="G73">
-        <v>-2.328152232797414</v>
+        <v>-2.626160921151528</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.707423215252347</v>
       </c>
       <c r="E74">
-        <v>-6.706092437394419</v>
+        <v>-5.951141478627679</v>
       </c>
       <c r="F74">
-        <v>1.951814746718244</v>
+        <v>0.8214272288082684</v>
       </c>
       <c r="G74">
-        <v>-2.00766162968611</v>
+        <v>-2.236128998442293</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.587949806361255</v>
       </c>
       <c r="E75">
-        <v>-5.724305687109463</v>
+        <v>-6.413113754520171</v>
       </c>
       <c r="F75">
-        <v>1.713386237442919</v>
+        <v>0.1866810653119687</v>
       </c>
       <c r="G75">
-        <v>-2.088336313932609</v>
+        <v>-2.133459049632875</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.462110682775725</v>
       </c>
       <c r="E76">
-        <v>-5.345385624517646</v>
+        <v>-4.896373841235107</v>
       </c>
       <c r="F76">
-        <v>1.211020467712288</v>
+        <v>0.4997670551470239</v>
       </c>
       <c r="G76">
-        <v>-0.9786215858956717</v>
+        <v>-2.836036266159164</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.335740117139672</v>
       </c>
       <c r="E77">
-        <v>-7.285356718559581</v>
+        <v>-8.096410941807349</v>
       </c>
       <c r="F77">
-        <v>1.355066439251083</v>
+        <v>0.9590243498593938</v>
       </c>
       <c r="G77">
-        <v>-0.6998504776702629</v>
+        <v>-0.6966458695882484</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.21353233346312</v>
       </c>
       <c r="E78">
-        <v>-7.174436276215704</v>
+        <v>-10.09043390160484</v>
       </c>
       <c r="F78">
-        <v>1.47641790502163</v>
+        <v>-0.166448928594973</v>
       </c>
       <c r="G78">
-        <v>-0.2072744068821029</v>
+        <v>-0.08414859718552894</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.100502832215194</v>
       </c>
       <c r="E79">
-        <v>-5.97953953912978</v>
+        <v>-9.203813032591075</v>
       </c>
       <c r="F79">
-        <v>1.177385721480185</v>
+        <v>0.5850797091058315</v>
       </c>
       <c r="G79">
-        <v>-1.071846548281548</v>
+        <v>-0.5608174966574908</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.002308308667899</v>
       </c>
       <c r="E80">
-        <v>-7.517128546746157</v>
+        <v>-9.598677852163899</v>
       </c>
       <c r="F80">
-        <v>1.703161832052842</v>
+        <v>-0.2295318944717148</v>
       </c>
       <c r="G80">
-        <v>-0.3009595350979383</v>
+        <v>-0.9412389056662215</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.923400943843657</v>
       </c>
       <c r="E81">
-        <v>-8.833392915711654</v>
+        <v>-9.142080874918513</v>
       </c>
       <c r="F81">
-        <v>0.773220804448207</v>
+        <v>0.07418568302055839</v>
       </c>
       <c r="G81">
-        <v>-0.03465925191896397</v>
+        <v>-0.5024161627992078</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.869071837711707</v>
       </c>
       <c r="E82">
-        <v>-8.759343308738229</v>
+        <v>-9.051312141908767</v>
       </c>
       <c r="F82">
-        <v>1.342821225112905</v>
+        <v>-0.1040414132911661</v>
       </c>
       <c r="G82">
-        <v>0.8278802145193689</v>
+        <v>0.3368402368614308</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.848098364446909</v>
       </c>
       <c r="E83">
-        <v>-10.23582961656911</v>
+        <v>-10.00317473595104</v>
       </c>
       <c r="F83">
-        <v>0.6156404821560665</v>
+        <v>0.386829818905206</v>
       </c>
       <c r="G83">
-        <v>1.357140440428193</v>
+        <v>0.6677623689669787</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.868822774837619</v>
       </c>
       <c r="E84">
-        <v>-11.867004068028</v>
+        <v>-10.52453341998012</v>
       </c>
       <c r="F84">
-        <v>1.312499591655901</v>
+        <v>-0.5215023333362159</v>
       </c>
       <c r="G84">
-        <v>1.445942513973603</v>
+        <v>1.299411147314382</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.93822928957047</v>
       </c>
       <c r="E85">
-        <v>-13.16793955247754</v>
+        <v>-12.51853826588158</v>
       </c>
       <c r="F85">
-        <v>1.150149147146457</v>
+        <v>-0.6133770727556468</v>
       </c>
       <c r="G85">
-        <v>1.441400445493723</v>
+        <v>-0.7348561862025164</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.06253246606966</v>
       </c>
       <c r="E86">
-        <v>-13.29764410500523</v>
+        <v>-14.9317530076211</v>
       </c>
       <c r="F86">
-        <v>0.4413473113382936</v>
+        <v>-0.8583565815501863</v>
       </c>
       <c r="G86">
-        <v>1.71913535296534</v>
+        <v>0.9661583911491871</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.245446155581616</v>
       </c>
       <c r="E87">
-        <v>-13.47701243197505</v>
+        <v>-15.75073206038229</v>
       </c>
       <c r="F87">
-        <v>0.2121375541967423</v>
+        <v>-0.1981547210220707</v>
       </c>
       <c r="G87">
-        <v>0.9356947510968137</v>
+        <v>2.718701609819647</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.487119597085011</v>
       </c>
       <c r="E88">
-        <v>-14.73690635649306</v>
+        <v>-16.95996141770249</v>
       </c>
       <c r="F88">
-        <v>0.7983304617374994</v>
+        <v>-0.9386900641108523</v>
       </c>
       <c r="G88">
-        <v>1.568340003651538</v>
+        <v>2.674323746865717</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.790847515975669</v>
       </c>
       <c r="E89">
-        <v>-17.10441973854717</v>
+        <v>-19.47838619606221</v>
       </c>
       <c r="F89">
-        <v>0.5584053503720848</v>
+        <v>-0.2390689714944912</v>
       </c>
       <c r="G89">
-        <v>1.274628403407398</v>
+        <v>2.585197239857457</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.157299416463466</v>
       </c>
       <c r="E90">
-        <v>-19.75729038172062</v>
+        <v>-18.07539702137582</v>
       </c>
       <c r="F90">
-        <v>0.4089518149850219</v>
+        <v>-1.176508054755775</v>
       </c>
       <c r="G90">
-        <v>1.747238574048213</v>
+        <v>2.271632298014309</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.582672866706322</v>
       </c>
       <c r="E91">
-        <v>-20.08811805035098</v>
+        <v>-23.60239954773749</v>
       </c>
       <c r="F91">
-        <v>0.3117098962181667</v>
+        <v>-1.313925425185498</v>
       </c>
       <c r="G91">
-        <v>1.649239804994707</v>
+        <v>-0.00955869564020983</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.059977537697377</v>
       </c>
       <c r="E92">
-        <v>-20.89441737589069</v>
+        <v>-22.94983285781017</v>
       </c>
       <c r="F92">
-        <v>0.2355376009503179</v>
+        <v>-1.930537364097058</v>
       </c>
       <c r="G92">
-        <v>1.233269757985283</v>
+        <v>2.482245894677202</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.579118148326289</v>
       </c>
       <c r="E93">
-        <v>-23.01299148479515</v>
+        <v>-24.69752041701241</v>
       </c>
       <c r="F93">
-        <v>-0.4892208638088559</v>
+        <v>-1.492416208532143</v>
       </c>
       <c r="G93">
-        <v>1.250967934438227</v>
+        <v>2.256450136171211</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.12176404161347</v>
       </c>
       <c r="E94">
-        <v>-24.84437882908116</v>
+        <v>-25.37400650664825</v>
       </c>
       <c r="F94">
-        <v>-0.493286236893789</v>
+        <v>-1.237514782177375</v>
       </c>
       <c r="G94">
-        <v>0.5837175493615011</v>
+        <v>0.9448782044227519</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.675519204229102</v>
       </c>
       <c r="E95">
-        <v>-25.66127931227283</v>
+        <v>-26.19130549555259</v>
       </c>
       <c r="F95">
-        <v>-0.6373860544337089</v>
+        <v>-1.73449357623664</v>
       </c>
       <c r="G95">
-        <v>0.9346519292519433</v>
+        <v>-0.1344887526556866</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.227526913697526</v>
       </c>
       <c r="E96">
-        <v>-29.69240686933978</v>
+        <v>-30.67967760164803</v>
       </c>
       <c r="F96">
-        <v>-0.6722046208376028</v>
+        <v>-1.109017635316365</v>
       </c>
       <c r="G96">
-        <v>1.002163884434301</v>
+        <v>0.8096159347792098</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.760600880139899</v>
       </c>
       <c r="E97">
-        <v>-31.03157852407308</v>
+        <v>-31.78794463096722</v>
       </c>
       <c r="F97">
-        <v>-0.806457746848278</v>
+        <v>-1.991331083073032</v>
       </c>
       <c r="G97">
-        <v>0.9813140686279707</v>
+        <v>-1.439926243519876</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.261975709005688</v>
       </c>
       <c r="E98">
-        <v>-34.06993778138647</v>
+        <v>-37.35861976065886</v>
       </c>
       <c r="F98">
-        <v>-1.143209054177745</v>
+        <v>-2.283025957108247</v>
       </c>
       <c r="G98">
-        <v>0.364675303755623</v>
+        <v>0.534532774284549</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.713834710999038</v>
       </c>
       <c r="E99">
-        <v>-36.64879051690455</v>
+        <v>-36.517990073667</v>
       </c>
       <c r="F99">
-        <v>-1.80080651032792</v>
+        <v>-2.907150205029694</v>
       </c>
       <c r="G99">
-        <v>-0.002596618371122524</v>
+        <v>-0.5396598001160087</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.10707114009387</v>
       </c>
       <c r="E100">
-        <v>-37.75134261202606</v>
+        <v>-39.13492953982659</v>
       </c>
       <c r="F100">
-        <v>-1.307360964166001</v>
+        <v>-2.692667329195814</v>
       </c>
       <c r="G100">
-        <v>0.03992071798973733</v>
+        <v>-1.20325203237184</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.42243914166295</v>
       </c>
       <c r="E101">
-        <v>-39.8902201341439</v>
+        <v>-40.33215617678945</v>
       </c>
       <c r="F101">
-        <v>-1.576348662785645</v>
+        <v>-2.949173049642922</v>
       </c>
       <c r="G101">
-        <v>-1.197958470054545</v>
+        <v>-1.504104479344187</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.67365657076396</v>
       </c>
       <c r="E102">
-        <v>-42.83788990674268</v>
+        <v>-40.84708895620165</v>
       </c>
       <c r="F102">
-        <v>-1.742302830105672</v>
+        <v>-3.247077634572575</v>
       </c>
       <c r="G102">
-        <v>-0.2435646070835937</v>
+        <v>-2.823929601122049</v>
       </c>
     </row>
   </sheetData>
